--- a/Employee_Reports_wi52/Crisfo Lo Nibal Q0489.xlsx
+++ b/Employee_Reports_wi52/Crisfo Lo Nibal Q0489.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1509,11 +1509,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1558,11 +1558,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1607,11 +1607,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1656,11 +1656,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1705,11 +1705,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1754,11 +1754,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1769,53 +1769,53 @@
       <c r="K27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Bin Hoist S-Type (DFW Trainings)</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>QDFWH</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>LSME-QDF-M-011</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>29-Sep-2024</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>29-Sep-2026</t>
         </is>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr"/>
+      <c r="H28" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -1852,11 +1852,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1901,11 +1901,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1950,11 +1950,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1999,11 +1999,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2048,11 +2048,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2097,11 +2097,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2195,11 +2195,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2244,11 +2244,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2293,11 +2293,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2342,11 +2342,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2391,11 +2391,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2440,11 +2440,11 @@
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>-21</v>
+        <v>-29</v>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -2489,11 +2489,11 @@
         </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -2538,11 +2538,11 @@
         </is>
       </c>
       <c r="H43" s="5" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -2587,11 +2587,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -2636,11 +2636,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -2673,11 +2673,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -2710,11 +2710,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7527</v>
+        <v>7519</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
